--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-11.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-11.xlsx
@@ -101,67 +101,67 @@
     <t>44</t>
   </si>
   <si>
-    <t>1,439,834,149.6</t>
-  </si>
-  <si>
-    <t>1,038,392,527.1</t>
-  </si>
-  <si>
-    <t>725,386,424.27</t>
-  </si>
-  <si>
-    <t>707,199,935.8</t>
-  </si>
-  <si>
-    <t>694,014,496.0</t>
-  </si>
-  <si>
-    <t>682,117,957.7</t>
-  </si>
-  <si>
-    <t>644,393,100.9</t>
-  </si>
-  <si>
-    <t>737,509,226.4</t>
-  </si>
-  <si>
-    <t>510,246,502.25</t>
-  </si>
-  <si>
-    <t>356,722,916.15</t>
-  </si>
-  <si>
-    <t>374,646,640.8</t>
-  </si>
-  <si>
-    <t>328,108,814.0</t>
-  </si>
-  <si>
-    <t>366,022,897.7</t>
-  </si>
-  <si>
-    <t>325,285,561.2</t>
-  </si>
-  <si>
-    <t>702,324,923.2</t>
-  </si>
-  <si>
-    <t>528,146,024.85</t>
-  </si>
-  <si>
-    <t>368,663,508.12</t>
-  </si>
-  <si>
-    <t>332,553,295.0</t>
-  </si>
-  <si>
-    <t>365,905,682.0</t>
-  </si>
-  <si>
-    <t>316,095,060.0</t>
-  </si>
-  <si>
-    <t>319,107,539.7</t>
+    <t>1,437,799,832.6</t>
+  </si>
+  <si>
+    <t>1,036,273,098.0</t>
+  </si>
+  <si>
+    <t>723,687,038.87</t>
+  </si>
+  <si>
+    <t>706,209,288.6</t>
+  </si>
+  <si>
+    <t>691,649,971.8</t>
+  </si>
+  <si>
+    <t>681,968,057.59</t>
+  </si>
+  <si>
+    <t>644,075,765.9</t>
+  </si>
+  <si>
+    <t>735,233,055.4</t>
+  </si>
+  <si>
+    <t>509,960,727.35</t>
+  </si>
+  <si>
+    <t>356,435,436.75</t>
+  </si>
+  <si>
+    <t>374,476,879.8</t>
+  </si>
+  <si>
+    <t>326,164,241.3</t>
+  </si>
+  <si>
+    <t>367,268,857.7</t>
+  </si>
+  <si>
+    <t>322,591,195.2</t>
+  </si>
+  <si>
+    <t>702,566,777.2</t>
+  </si>
+  <si>
+    <t>526,312,370.65</t>
+  </si>
+  <si>
+    <t>367,251,602.12</t>
+  </si>
+  <si>
+    <t>331,732,408.8</t>
+  </si>
+  <si>
+    <t>365,485,730.5</t>
+  </si>
+  <si>
+    <t>314,699,199.89</t>
+  </si>
+  <si>
+    <t>321,484,570.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,7 +182,7 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>78,488,556.7</t>
+    <t>77,485,966.7</t>
   </si>
   <si>
     <t>MFIL</t>
@@ -206,13 +206,13 @@
     <t>MBJC</t>
   </si>
   <si>
-    <t>29,010,798.6</t>
+    <t>28,831,970.6</t>
   </si>
   <si>
     <t>SHPC</t>
   </si>
   <si>
-    <t>63,419,784.5</t>
+    <t>63,286,129.3</t>
   </si>
   <si>
     <t>LSL</t>
@@ -230,7 +230,7 @@
     <t>AHPC</t>
   </si>
   <si>
-    <t>13,284,068.8</t>
+    <t>13,231,986.5</t>
   </si>
   <si>
     <t>SGIC</t>
@@ -263,16 +263,16 @@
     <t>8,323,948.9</t>
   </si>
   <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>13,097,431.2</t>
+  </si>
+  <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>13,500,450.9</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>13,097,431.2</t>
+    <t>13,055,450.9</t>
   </si>
   <si>
     <t>PCBL</t>
@@ -287,7 +287,7 @@
     <t>12,385,898.7</t>
   </si>
   <si>
-    <t>10,456,770.19</t>
+    <t>10,591,770.19</t>
   </si>
   <si>
     <t>14,323,676.8</t>
@@ -299,7 +299,7 @@
     <t>12,366,595.5</t>
   </si>
   <si>
-    <t>9,372,509.9</t>
+    <t>9,381,429.9</t>
   </si>
   <si>
     <t>EHPL</t>
@@ -311,13 +311,13 @@
     <t>8,171,033.5</t>
   </si>
   <si>
-    <t>13,687,360.0</t>
-  </si>
-  <si>
-    <t>12,127,624.8</t>
-  </si>
-  <si>
-    <t>12,080,125.3</t>
+    <t>13,688,770.0</t>
+  </si>
+  <si>
+    <t>13,267,624.8</t>
+  </si>
+  <si>
+    <t>12,082,168.3</t>
   </si>
   <si>
     <t>HURJA</t>
@@ -335,7 +335,7 @@
     <t>UAIL</t>
   </si>
   <si>
-    <t>12,950,627.1</t>
+    <t>12,307,226.3</t>
   </si>
   <si>
     <t>HIDCLP</t>
@@ -347,7 +347,7 @@
     <t>NICA</t>
   </si>
   <si>
-    <t>11,889,324.6</t>
+    <t>11,353,705.6</t>
   </si>
   <si>
     <t>SPDL</t>
@@ -359,7 +359,7 @@
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>125,378,142.1</t>
+    <t>126,552,312.1</t>
   </si>
   <si>
     <t>NTC</t>
@@ -383,15 +383,15 @@
     <t>57,718,104.5</t>
   </si>
   <si>
-    <t>21,187,679.2</t>
-  </si>
-  <si>
-    <t>11,884,493.9</t>
+    <t>21,218,099.2</t>
   </si>
   <si>
     <t>10,426,795.8</t>
   </si>
   <si>
+    <t>9,986,453.69</t>
+  </si>
+  <si>
     <t>NHDL</t>
   </si>
   <si>
@@ -404,22 +404,22 @@
     <t>11,816,226.5</t>
   </si>
   <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>10,458,910.5</t>
+  </si>
+  <si>
     <t>SBL</t>
   </si>
   <si>
-    <t>10,507,059.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>10,458,910.5</t>
+    <t>10,219,684.0</t>
   </si>
   <si>
     <t>BNHC</t>
   </si>
   <si>
-    <t>9,390,297.1</t>
+    <t>9,410,297.1</t>
   </si>
   <si>
     <t>NUBL</t>
@@ -443,10 +443,10 @@
     <t>JFL</t>
   </si>
   <si>
-    <t>6,779,097.2</t>
-  </si>
-  <si>
-    <t>10,404,661.1</t>
+    <t>6,753,753.2</t>
+  </si>
+  <si>
+    <t>10,636,201.1</t>
   </si>
   <si>
     <t>9,572,315.9</t>
@@ -476,7 +476,7 @@
     <t>SRLI</t>
   </si>
   <si>
-    <t>8,845,867.0</t>
+    <t>8,522,467.0</t>
   </si>
   <si>
     <t>6,764,447.9</t>
@@ -509,7 +509,7 @@
     <t>SBI</t>
   </si>
   <si>
-    <t>12,440,115.4</t>
+    <t>12,622,895.4</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -527,91 +527,91 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>378,253,723.2</t>
-  </si>
-  <si>
-    <t>262,670,411.3</t>
-  </si>
-  <si>
-    <t>248,236,780.2</t>
-  </si>
-  <si>
-    <t>227,434,601.2</t>
-  </si>
-  <si>
-    <t>216,626,277.4</t>
+    <t>381,787,244.7</t>
+  </si>
+  <si>
+    <t>261,535,594.3</t>
+  </si>
+  <si>
+    <t>251,069,025.5</t>
+  </si>
+  <si>
+    <t>227,671,702.8</t>
+  </si>
+  <si>
+    <t>217,849,043.4</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>3,663,566,831.4</t>
+    <t>3,669,645,030.0</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>2,549,344,184.98</t>
+    <t>2,541,128,768.79</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,324,681,808.2</t>
+    <t>1,324,832,073.2</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>855,991,628.8</t>
+    <t>853,799,201.0</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>809,513,463.0</t>
+    <t>806,609,715.6</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>577,729,904.6</t>
+    <t>576,238,119.7</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>469,802,782.2</t>
+    <t>468,005,588.6</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>409,956,941.1</t>
+    <t>409,870,066.6</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>228,309,772.5</t>
+    <t>227,585,428.5</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>175,756,143.9</t>
+    <t>175,099,239.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>124,161,901.7</t>
+    <t>123,480,229.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>111,692,121.6</t>
+    <t>111,572,007.2</t>
   </si>
   <si>
     <t>Trading</t>
@@ -623,7 +623,7 @@
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>8,084,684.0</t>
+    <t>8,078,201.0</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -641,208 +641,208 @@
     <t>100%</t>
   </si>
   <si>
-    <t>226,750,296.8</t>
-  </si>
-  <si>
-    <t>119,402,756.1</t>
-  </si>
-  <si>
-    <t>102,381,221.6</t>
-  </si>
-  <si>
-    <t>101,652,500.7</t>
-  </si>
-  <si>
-    <t>57,653,489.5</t>
-  </si>
-  <si>
-    <t>183,177,507.0</t>
-  </si>
-  <si>
-    <t>156,610,615.55</t>
-  </si>
-  <si>
-    <t>46,172,784.4</t>
-  </si>
-  <si>
-    <t>32,398,927.0</t>
-  </si>
-  <si>
-    <t>24,994,652.0</t>
-  </si>
-  <si>
-    <t>120,428,793.0</t>
-  </si>
-  <si>
-    <t>62,002,412.45</t>
+    <t>226,431,411.8</t>
+  </si>
+  <si>
+    <t>118,400,166.1</t>
+  </si>
+  <si>
+    <t>102,300,444.6</t>
+  </si>
+  <si>
+    <t>101,633,301.7</t>
+  </si>
+  <si>
+    <t>57,643,129.5</t>
+  </si>
+  <si>
+    <t>183,858,136.5</t>
+  </si>
+  <si>
+    <t>156,184,317.55</t>
+  </si>
+  <si>
+    <t>46,181,584.4</t>
+  </si>
+  <si>
+    <t>31,949,577.0</t>
+  </si>
+  <si>
+    <t>25,728,817.0</t>
+  </si>
+  <si>
+    <t>120,538,969.6</t>
+  </si>
+  <si>
+    <t>61,488,816.45</t>
   </si>
   <si>
     <t>45,173,601.7</t>
   </si>
   <si>
-    <t>38,208,260.79</t>
-  </si>
-  <si>
-    <t>27,102,456.0</t>
-  </si>
-  <si>
-    <t>119,812,630.8</t>
-  </si>
-  <si>
-    <t>90,916,785.2</t>
-  </si>
-  <si>
-    <t>38,115,642.2</t>
+    <t>38,301,450.79</t>
+  </si>
+  <si>
+    <t>27,048,566.0</t>
+  </si>
+  <si>
+    <t>119,912,854.8</t>
+  </si>
+  <si>
+    <t>90,372,528.2</t>
+  </si>
+  <si>
+    <t>38,113,641.2</t>
   </si>
   <si>
     <t>28,163,817.3</t>
   </si>
   <si>
-    <t>24,035,794.1</t>
-  </si>
-  <si>
-    <t>109,241,194.7</t>
-  </si>
-  <si>
-    <t>73,489,346.2</t>
-  </si>
-  <si>
-    <t>29,121,702.5</t>
-  </si>
-  <si>
-    <t>29,000,704.9</t>
-  </si>
-  <si>
-    <t>26,476,215.3</t>
-  </si>
-  <si>
-    <t>136,053,046.0</t>
-  </si>
-  <si>
-    <t>70,803,936.8</t>
-  </si>
-  <si>
-    <t>52,772,989.5</t>
+    <t>24,093,442.1</t>
+  </si>
+  <si>
+    <t>108,946,578.0</t>
+  </si>
+  <si>
+    <t>73,089,863.7</t>
+  </si>
+  <si>
+    <t>28,994,196.5</t>
+  </si>
+  <si>
+    <t>27,903,029.9</t>
+  </si>
+  <si>
+    <t>26,460,122.8</t>
+  </si>
+  <si>
+    <t>137,546,613.5</t>
+  </si>
+  <si>
+    <t>70,742,951.8</t>
+  </si>
+  <si>
+    <t>53,063,782.5</t>
   </si>
   <si>
     <t>31,987,649.3</t>
   </si>
   <si>
-    <t>20,337,147.89</t>
-  </si>
-  <si>
-    <t>115,130,916.8</t>
-  </si>
-  <si>
-    <t>69,412,860.09</t>
-  </si>
-  <si>
-    <t>31,085,267.9</t>
-  </si>
-  <si>
-    <t>29,838,390.2</t>
-  </si>
-  <si>
-    <t>26,112,000.7</t>
-  </si>
-  <si>
-    <t>291,939,043.0</t>
-  </si>
-  <si>
-    <t>110,122,599.4</t>
+    <t>20,249,782.89</t>
+  </si>
+  <si>
+    <t>115,295,068.8</t>
+  </si>
+  <si>
+    <t>68,372,284.3</t>
+  </si>
+  <si>
+    <t>30,994,271.9</t>
+  </si>
+  <si>
+    <t>29,302,771.2</t>
+  </si>
+  <si>
+    <t>26,118,894.7</t>
+  </si>
+  <si>
+    <t>293,192,764.0</t>
+  </si>
+  <si>
+    <t>110,220,834.4</t>
   </si>
   <si>
     <t>62,864,790.2</t>
   </si>
   <si>
-    <t>57,453,981.1</t>
-  </si>
-  <si>
-    <t>53,823,683.9</t>
-  </si>
-  <si>
-    <t>201,658,216.2</t>
-  </si>
-  <si>
-    <t>89,725,015.6</t>
-  </si>
-  <si>
-    <t>80,081,859.45</t>
-  </si>
-  <si>
-    <t>50,329,068.0</t>
-  </si>
-  <si>
-    <t>38,905,243.6</t>
-  </si>
-  <si>
-    <t>148,432,451.0</t>
-  </si>
-  <si>
-    <t>61,670,531.3</t>
+    <t>56,966,236.1</t>
+  </si>
+  <si>
+    <t>53,011,394.9</t>
+  </si>
+  <si>
+    <t>200,136,596.9</t>
+  </si>
+  <si>
+    <t>89,730,815.6</t>
+  </si>
+  <si>
+    <t>80,118,344.95</t>
+  </si>
+  <si>
+    <t>50,244,568.0</t>
+  </si>
+  <si>
+    <t>38,867,493.6</t>
+  </si>
+  <si>
+    <t>147,803,812.0</t>
+  </si>
+  <si>
+    <t>61,634,645.3</t>
   </si>
   <si>
     <t>49,282,307.5</t>
   </si>
   <si>
-    <t>30,526,652.2</t>
-  </si>
-  <si>
-    <t>26,446,881.7</t>
-  </si>
-  <si>
-    <t>84,552,343.0</t>
-  </si>
-  <si>
-    <t>83,947,904.09</t>
-  </si>
-  <si>
-    <t>44,378,037.3</t>
-  </si>
-  <si>
-    <t>43,543,860.5</t>
-  </si>
-  <si>
-    <t>19,076,974.5</t>
-  </si>
-  <si>
-    <t>116,835,327.4</t>
-  </si>
-  <si>
-    <t>85,101,992.4</t>
+    <t>30,193,889.2</t>
+  </si>
+  <si>
+    <t>26,201,645.7</t>
+  </si>
+  <si>
+    <t>84,005,259.09</t>
+  </si>
+  <si>
+    <t>83,939,955.09</t>
+  </si>
+  <si>
+    <t>44,851,533.5</t>
+  </si>
+  <si>
+    <t>43,624,360.5</t>
+  </si>
+  <si>
+    <t>18,753,935.0</t>
+  </si>
+  <si>
+    <t>116,628,477.4</t>
+  </si>
+  <si>
+    <t>85,160,142.7</t>
   </si>
   <si>
     <t>38,779,341.79</t>
   </si>
   <si>
-    <t>33,982,789.9</t>
+    <t>33,711,538.1</t>
   </si>
   <si>
     <t>29,269,958.2</t>
   </si>
   <si>
-    <t>99,546,848.6</t>
-  </si>
-  <si>
-    <t>69,149,013.7</t>
-  </si>
-  <si>
-    <t>49,849,372.1</t>
-  </si>
-  <si>
-    <t>28,844,894.9</t>
-  </si>
-  <si>
-    <t>23,005,837.5</t>
-  </si>
-  <si>
-    <t>123,612,195.1</t>
-  </si>
-  <si>
-    <t>72,490,314.0</t>
-  </si>
-  <si>
-    <t>30,009,522.4</t>
+    <t>99,512,733.4</t>
+  </si>
+  <si>
+    <t>68,589,429.7</t>
+  </si>
+  <si>
+    <t>49,726,788.1</t>
+  </si>
+  <si>
+    <t>28,797,292.4</t>
+  </si>
+  <si>
+    <t>22,731,303.1</t>
+  </si>
+  <si>
+    <t>123,640,630.1</t>
+  </si>
+  <si>
+    <t>74,679,524.0</t>
+  </si>
+  <si>
+    <t>30,192,302.4</t>
   </si>
   <si>
     <t>24,982,550.6</t>
@@ -1657,7 +1657,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.05451222053720902</v>
+        <v>0.05389204042393071</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1666,7 +1666,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.06107496235274092</v>
+        <v>0.06107089860977941</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>54</v>
@@ -1675,7 +1675,7 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.05340627382017327</v>
+        <v>0.05353168416625342</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>82</v>
@@ -1684,7 +1684,7 @@
         <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.01909000583367983</v>
+        <v>0.01854610440761059</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>70</v>
@@ -1693,7 +1693,7 @@
         <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.0206388726497148</v>
+        <v>0.02070943018001292</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>70</v>
@@ -1702,7 +1702,7 @@
         <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.02006597223470224</v>
+        <v>0.0200724503845149</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>80</v>
@@ -1711,7 +1711,7 @@
         <v>104</v>
       </c>
       <c r="V9" s="18">
-        <v>0.08158247120674597</v>
+        <v>0.08162266674719489</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1723,7 +1723,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0422561216629724</v>
+        <v>0.04231590908588342</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1732,7 +1732,7 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04553576414119015</v>
+        <v>0.04562889579132932</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>70</v>
@@ -1741,7 +1741,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02552620793618261</v>
+        <v>0.02558614940639582</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>84</v>
@@ -1750,7 +1750,7 @@
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.01852012498443442</v>
+        <v>0.01848665984821769</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>92</v>
@@ -1759,7 +1759,7 @@
         <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01781892967837951</v>
+        <v>0.01787984674938434</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>88</v>
@@ -1768,7 +1768,7 @@
         <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01777936596317232</v>
+        <v>0.01945490650499347</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>105</v>
@@ -1777,7 +1777,7 @@
         <v>106</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02009740185286332</v>
+        <v>0.01910835176790495</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1789,7 +1789,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03138875704021571</v>
+        <v>0.03143316842531117</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1798,7 +1798,7 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03526043566805634</v>
+        <v>0.03533255178645967</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1807,7 +1807,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01475176615108118</v>
+        <v>0.01478640672729007</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>86</v>
@@ -1816,16 +1816,16 @@
         <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01799898141336907</v>
+        <v>0.01802422979345673</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01350477541033956</v>
+        <v>0.01356384050097637</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>78</v>
@@ -1834,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01770973064648874</v>
+        <v>0.01771661907820124</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>107</v>
@@ -1843,7 +1843,7 @@
         <v>108</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01856623896700692</v>
+        <v>0.01857538652037646</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1855,7 +1855,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02241030017864496</v>
+        <v>0.02244200810738083</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1864,7 +1864,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01279291641003952</v>
+        <v>0.0127688217763615</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1873,7 +1873,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0120512848152589</v>
+        <v>0.0120795840335208</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>88</v>
@@ -1882,7 +1882,7 @@
         <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01751399862047329</v>
+        <v>0.01753856668262463</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>95</v>
@@ -1891,7 +1891,7 @@
         <v>96</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01251541149365272</v>
+        <v>0.01255819757701319</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>101</v>
@@ -1900,7 +1900,7 @@
         <v>102</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01398919379307231</v>
+        <v>0.01399226869009297</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>109</v>
@@ -1909,7 +1909,7 @@
         <v>110</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01845042192940089</v>
+        <v>0.01762790373603777</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1921,7 +1921,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02014870852178321</v>
+        <v>0.02005284042067429</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1930,7 +1930,7 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.009764248909144523</v>
+        <v>0.009784219159571389</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>80</v>
@@ -1939,7 +1939,7 @@
         <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01147519256150526</v>
+        <v>0.0115021389812334</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>76</v>
@@ -1948,7 +1948,7 @@
         <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01478615829930905</v>
+        <v>0.01499806129851008</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>72</v>
@@ -1957,7 +1957,7 @@
         <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01177357756515795</v>
+        <v>0.01181382756184477</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>72</v>
@@ -1966,7 +1966,7 @@
         <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01383607203631314</v>
+        <v>0.01383911327638111</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>111</v>
@@ -1975,7 +1975,7 @@
         <v>112</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01626646418988686</v>
+        <v>0.01627447864825805</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2055,7 +2055,7 @@
         <v>114</v>
       </c>
       <c r="D16" s="10">
-        <v>0.08707818336912712</v>
+        <v>0.08801803229532522</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>64</v>
@@ -2064,7 +2064,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="12">
-        <v>0.06963617525440491</v>
+        <v>0.06977859807376761</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>125</v>
@@ -2073,7 +2073,7 @@
         <v>126</v>
       </c>
       <c r="J16" s="14">
-        <v>0.03335149761638646</v>
+        <v>0.03342981468588369</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>135</v>
@@ -2082,7 +2082,7 @@
         <v>136</v>
       </c>
       <c r="M16" s="16">
-        <v>0.02082538579891087</v>
+        <v>0.02085459896625891</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>101</v>
@@ -2091,7 +2091,7 @@
         <v>143</v>
       </c>
       <c r="P16" s="18">
-        <v>0.01499199391362569</v>
+        <v>0.01537801132604629</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>70</v>
@@ -2100,16 +2100,16 @@
         <v>150</v>
       </c>
       <c r="S16" s="16">
-        <v>0.03284469723615371</v>
+        <v>0.03285191667018043</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U16" s="17" t="s">
         <v>157</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03549378875729053</v>
+        <v>0.03551127648474688</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2121,7 +2121,7 @@
         <v>116</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04294566309402945</v>
+        <v>0.04300642613665025</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>86</v>
@@ -2130,7 +2130,7 @@
         <v>121</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05558409078808942</v>
+        <v>0.05569777369633116</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>127</v>
@@ -2139,16 +2139,16 @@
         <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01628956112859622</v>
+        <v>0.01632781280489758</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>137</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01331245765647594</v>
+        <v>0.01333113193493048</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>88</v>
@@ -2157,7 +2157,7 @@
         <v>144</v>
       </c>
       <c r="P17" s="18">
-        <v>0.01379267429595592</v>
+        <v>0.01383982692153997</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>141</v>
@@ -2166,7 +2166,7 @@
         <v>151</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01525244553754401</v>
+        <v>0.01525579810382017</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>158</v>
@@ -2175,7 +2175,7 @@
         <v>159</v>
       </c>
       <c r="V17" s="18">
-        <v>0.02669087219583545</v>
+        <v>0.02670402274174433</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2187,7 +2187,7 @@
         <v>117</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03058587998640979</v>
+        <v>0.03062915539527098</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>58</v>
@@ -2196,7 +2196,7 @@
         <v>122</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02040430631677646</v>
+        <v>0.0204753932539123</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>129</v>
@@ -2205,7 +2205,7 @@
         <v>130</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01448477480202898</v>
+        <v>0.01445225620778154</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>78</v>
@@ -2214,7 +2214,7 @@
         <v>138</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01115258486424766</v>
+        <v>0.0111682293440738</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>145</v>
@@ -2223,7 +2223,7 @@
         <v>146</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01303692653705031</v>
+        <v>0.01308149550914216</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>152</v>
@@ -2232,7 +2232,7 @@
         <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01296823650535011</v>
+        <v>0.012496871231759</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>160</v>
@@ -2241,7 +2241,7 @@
         <v>161</v>
       </c>
       <c r="V18" s="18">
-        <v>0.023571328555172</v>
+        <v>0.02358294210740153</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2253,16 +2253,16 @@
         <v>118</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02351765459195913</v>
+        <v>0.02355092929644288</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>123</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0114450880469939</v>
+        <v>0.01006182233247553</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>131</v>
@@ -2271,7 +2271,7 @@
         <v>132</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01441839845641643</v>
+        <v>0.01412168997244653</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>139</v>
@@ -2280,7 +2280,7 @@
         <v>140</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01008325939952666</v>
+        <v>0.0100974038647047</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>147</v>
@@ -2289,16 +2289,16 @@
         <v>148</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01303499718253724</v>
+        <v>0.01307955955879936</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="R19" s="15" t="s">
         <v>154</v>
       </c>
       <c r="S19" s="16">
-        <v>0.009916830107814063</v>
+        <v>0.009919009878271462</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>60</v>
@@ -2307,7 +2307,7 @@
         <v>162</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02001447731514656</v>
+        <v>0.02002433841300968</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2319,16 +2319,16 @@
         <v>119</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01086579847015458</v>
+        <v>0.01088117229204913</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>124</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01004128547527179</v>
+        <v>0.00963689371004013</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>133</v>
@@ -2337,7 +2337,7 @@
         <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01294523413427543</v>
+        <v>0.01300326880897811</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>141</v>
@@ -2346,7 +2346,7 @@
         <v>142</v>
       </c>
       <c r="M20" s="16">
-        <v>0.009585828358894486</v>
+        <v>0.009563387665699984</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>70</v>
@@ -2355,7 +2355,7 @@
         <v>149</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01233572893555238</v>
+        <v>0.01237790074323256</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>155</v>
@@ -2364,7 +2364,7 @@
         <v>156</v>
       </c>
       <c r="S20" s="16">
-        <v>0.009777934776104195</v>
+        <v>0.009780084016650578</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>163</v>
@@ -2373,7 +2373,7 @@
         <v>164</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01930516540699358</v>
+        <v>0.01959846351672832</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2394,7 +2394,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>171</v>
@@ -2443,7 +2443,7 @@
         <v>176</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3237737312496003</v>
+        <v>0.3243109020262137</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2454,7 +2454,7 @@
         <v>178</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2253024762477883</v>
+        <v>0.2245764253582442</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2465,7 +2465,7 @@
         <v>180</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1170709288236137</v>
+        <v>0.1170842087395987</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2476,7 +2476,7 @@
         <v>182</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07564966502032919</v>
+        <v>0.07545590561536426</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2487,7 +2487,7 @@
         <v>184</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07154208083932684</v>
+        <v>0.07128545739731772</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2498,7 +2498,7 @@
         <v>186</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05105782847022247</v>
+        <v>0.05092598953141697</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2509,7 +2509,7 @@
         <v>188</v>
       </c>
       <c r="D37" s="22">
-        <v>0.0415195919017014</v>
+        <v>0.04136076196780675</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2520,7 +2520,7 @@
         <v>190</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0362306174774753</v>
+        <v>0.03622293980096224</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2531,7 +2531,7 @@
         <v>192</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02017725083912943</v>
+        <v>0.02011323574936003</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2542,7 +2542,7 @@
         <v>194</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01553273766232862</v>
+        <v>0.01547468269323951</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2553,7 +2553,7 @@
         <v>196</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01097301183314101</v>
+        <v>0.01091276790721516</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2564,7 +2564,7 @@
         <v>198</v>
       </c>
       <c r="D42" s="22">
-        <v>0.009870974551813134</v>
+        <v>0.009860359244585356</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2586,7 +2586,7 @@
         <v>202</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0007144972168157904</v>
+        <v>0.0007139242710511053</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2993,7 +2993,7 @@
         <v>208</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1574836218900583</v>
+        <v>0.1574846558373428</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>175</v>
@@ -3002,7 +3002,7 @@
         <v>213</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1764048779430011</v>
+        <v>0.1774224737232347</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>175</v>
@@ -3011,7 +3011,7 @@
         <v>218</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1660201914051462</v>
+        <v>0.1665622888427232</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>175</v>
@@ -3020,7 +3020,7 @@
         <v>223</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1694183281626933</v>
+        <v>0.169797900899487</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>175</v>
@@ -3029,7 +3029,7 @@
         <v>228</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1574047737181559</v>
+        <v>0.1575169268300113</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>175</v>
@@ -3038,7 +3038,7 @@
         <v>233</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1994567720497354</v>
+        <v>0.2016906979251458</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>175</v>
@@ -3047,7 +3047,7 @@
         <v>238</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1786656570953365</v>
+        <v>0.1790085497765815</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3059,7 +3059,7 @@
         <v>209</v>
       </c>
       <c r="D10" s="10">
-        <v>0.08292813178043544</v>
+        <v>0.0823481568264581</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>177</v>
@@ -3068,7 +3068,7 @@
         <v>214</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1508202451989699</v>
+        <v>0.1507173329611998</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>177</v>
@@ -3077,7 +3077,7 @@
         <v>219</v>
       </c>
       <c r="J10" s="14">
-        <v>0.08547501080185883</v>
+        <v>0.08496603248002288</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>177</v>
@@ -3086,7 +3086,7 @@
         <v>224</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1285588142724489</v>
+        <v>0.1279684785499719</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>177</v>
@@ -3095,7 +3095,7 @@
         <v>229</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1058902178896275</v>
+        <v>0.1056746427817898</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>177</v>
@@ -3104,7 +3104,7 @@
         <v>234</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1038001360332754</v>
+        <v>0.1037335268296296</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>177</v>
@@ -3113,7 +3113,7 @@
         <v>239</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1077181925179733</v>
+        <v>0.1061556542256483</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3125,7 +3125,7 @@
         <v>210</v>
       </c>
       <c r="D11" s="10">
-        <v>0.07110626014006023</v>
+        <v>0.07115068612506945</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>179</v>
@@ -3134,7 +3134,7 @@
         <v>215</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04446563625505891</v>
+        <v>0.04456507120481092</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>187</v>
@@ -3143,7 +3143,7 @@
         <v>220</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06227522350650678</v>
+        <v>0.06242146020818094</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>179</v>
@@ -3152,7 +3152,7 @@
         <v>225</v>
       </c>
       <c r="M11" s="16">
-        <v>0.05389655777737417</v>
+        <v>0.05396932866113537</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>181</v>
@@ -3161,7 +3161,7 @@
         <v>230</v>
       </c>
       <c r="P11" s="18">
-        <v>0.04196123087895847</v>
+        <v>0.04192033207858507</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>179</v>
@@ -3170,7 +3170,7 @@
         <v>235</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07736636882855664</v>
+        <v>0.07780977702495843</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>181</v>
@@ -3179,7 +3179,7 @@
         <v>240</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04823960383279144</v>
+        <v>0.04812208988594707</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3191,7 +3191,7 @@
         <v>211</v>
       </c>
       <c r="D12" s="10">
-        <v>0.07060014566833275</v>
+        <v>0.07068668349767063</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>181</v>
@@ -3200,7 +3200,7 @@
         <v>216</v>
       </c>
       <c r="G12" s="12">
-        <v>0.0312010402178866</v>
+        <v>0.03083123267569376</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>179</v>
@@ -3209,7 +3209,7 @@
         <v>221</v>
       </c>
       <c r="J12" s="14">
-        <v>0.05267297473681186</v>
+        <v>0.05292543425927005</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>183</v>
@@ -3218,7 +3218,7 @@
         <v>226</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03982440590600518</v>
+        <v>0.03988027027488179</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>179</v>
@@ -3227,7 +3227,7 @@
         <v>231</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04178688639379659</v>
+        <v>0.04034270373406238</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>181</v>
@@ -3236,7 +3236,7 @@
         <v>236</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04689460076356526</v>
+        <v>0.0469049084389257</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>183</v>
@@ -3245,7 +3245,7 @@
         <v>241</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04630463944807265</v>
+        <v>0.0454958449788182</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3257,7 +3257,7 @@
         <v>212</v>
       </c>
       <c r="D13" s="10">
-        <v>0.04004175725101166</v>
+        <v>0.04009120615611901</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>183</v>
@@ -3266,7 +3266,7 @@
         <v>217</v>
       </c>
       <c r="G13" s="12">
-        <v>0.0240705237640765</v>
+        <v>0.02482822052377548</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>183</v>
@@ -3275,7 +3275,7 @@
         <v>222</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03736278360499348</v>
+        <v>0.03737605421569376</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>189</v>
@@ -3284,7 +3284,7 @@
         <v>227</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03398726849827862</v>
+        <v>0.03411657491472989</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>183</v>
@@ -3293,7 +3293,7 @@
         <v>232</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03814936928925473</v>
+        <v>0.03825652263259444</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>183</v>
@@ -3302,7 +3302,7 @@
         <v>237</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02981470824866395</v>
+        <v>0.02969315450237299</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>179</v>
@@ -3311,7 +3311,7 @@
         <v>242</v>
       </c>
       <c r="V13" s="18">
-        <v>0.04052185019288744</v>
+        <v>0.040552518947057</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3391,7 +3391,7 @@
         <v>243</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2027587990471705</v>
+        <v>0.2039176506717309</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>175</v>
@@ -3400,7 +3400,7 @@
         <v>248</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1942022991663727</v>
+        <v>0.1931311324073377</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>175</v>
@@ -3409,7 +3409,7 @@
         <v>253</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2046253500668647</v>
+        <v>0.204237196552239</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>175</v>
@@ -3418,7 +3418,7 @@
         <v>258</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1195593193943839</v>
+        <v>0.1189523565549998</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>175</v>
@@ -3427,7 +3427,7 @@
         <v>263</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1683470994819105</v>
+        <v>0.1686235554907602</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>175</v>
@@ -3436,7 +3436,7 @@
         <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1459378799169239</v>
+        <v>0.145919933186032</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>177</v>
@@ -3445,7 +3445,7 @@
         <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1918273099562292</v>
+        <v>0.1919659714680161</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3457,7 +3457,7 @@
         <v>244</v>
       </c>
       <c r="D17" s="10">
-        <v>0.076482836186788</v>
+        <v>0.07665937351007034</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>183</v>
@@ -3466,7 +3466,7 @@
         <v>249</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08640760912502141</v>
+        <v>0.08658993056287947</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>177</v>
@@ -3475,7 +3475,7 @@
         <v>254</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08501748755783893</v>
+        <v>0.08516754064884086</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>177</v>
@@ -3484,7 +3484,7 @@
         <v>259</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1187046263020885</v>
+        <v>0.1188598853838411</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>177</v>
@@ -3493,7 +3493,7 @@
         <v>264</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1226227879828032</v>
+        <v>0.1231260697927495</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>177</v>
@@ -3502,7 +3502,7 @@
         <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1013739821968038</v>
+        <v>0.1005757218914061</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>175</v>
@@ -3511,7 +3511,7 @@
         <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1124939325060362</v>
+        <v>0.1159483525911683</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3523,7 +3523,7 @@
         <v>245</v>
       </c>
       <c r="D18" s="10">
-        <v>0.04366113292802817</v>
+        <v>0.04372290827598752</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>177</v>
@@ -3532,7 +3532,7 @@
         <v>250</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07712098976063596</v>
+        <v>0.07731392921868556</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>179</v>
@@ -3541,7 +3541,7 @@
         <v>255</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06793938492796546</v>
+        <v>0.06809892239738297</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>179</v>
@@ -3550,7 +3550,7 @@
         <v>260</v>
       </c>
       <c r="M18" s="16">
-        <v>0.06275175527243028</v>
+        <v>0.06351025712068212</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>179</v>
@@ -3559,7 +3559,7 @@
         <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05587684698735745</v>
+        <v>0.05606787158405838</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>179</v>
@@ -3568,7 +3568,7 @@
         <v>270</v>
       </c>
       <c r="S18" s="16">
-        <v>0.07308028111161982</v>
+        <v>0.07291659418037823</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>183</v>
@@ -3577,7 +3577,7 @@
         <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04657021057191148</v>
+        <v>0.04687694212156974</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3589,7 +3589,7 @@
         <v>246</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03990319379211924</v>
+        <v>0.03962042198668705</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>179</v>
@@ -3598,7 +3598,7 @@
         <v>251</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04846824942062895</v>
+        <v>0.04848583650098769</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>183</v>
@@ -3607,7 +3607,7 @@
         <v>256</v>
       </c>
       <c r="J19" s="14">
-        <v>0.04208329681758355</v>
+        <v>0.04172230201489611</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>181</v>
@@ -3616,7 +3616,7 @@
         <v>261</v>
       </c>
       <c r="M19" s="16">
-        <v>0.06157220652281627</v>
+        <v>0.06177256686396974</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>181</v>
@@ -3625,7 +3625,7 @@
         <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04896553327900516</v>
+        <v>0.04874074961973417</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>181</v>
@@ -3634,7 +3634,7 @@
         <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04228725336195616</v>
+        <v>0.04222674666221787</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>181</v>
@@ -3643,7 +3643,7 @@
         <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0387691155679783</v>
+        <v>0.03878821704320858</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3655,7 +3655,7 @@
         <v>247</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03738186367850266</v>
+        <v>0.03686980183057785</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>181</v>
@@ -3664,7 +3664,7 @@
         <v>252</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03746679852237932</v>
+        <v>0.03750699856535309</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>181</v>
@@ -3673,7 +3673,7 @@
         <v>257</v>
       </c>
       <c r="J20" s="14">
-        <v>0.03645902489368352</v>
+        <v>0.03620576892037823</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>183</v>
@@ -3682,7 +3682,7 @@
         <v>262</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02697536231874754</v>
+        <v>0.02655577504110444</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>183</v>
@@ -3691,7 +3691,7 @@
         <v>267</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04217485134489179</v>
+        <v>0.04231903331655713</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>183</v>
@@ -3700,7 +3700,7 @@
         <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03372706617719353</v>
+        <v>0.0333319175974262</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>179</v>
@@ -3709,7 +3709,7 @@
         <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02977514885432877</v>
+        <v>0.02978981901793675</v>
       </c>
     </row>
   </sheetData>
